--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92494</v>
+        <v>92497</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -793,7 +793,7 @@
         <v>136247735</v>
       </c>
       <c r="B3" t="n">
-        <v>83341</v>
+        <v>83343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>136247010</v>
       </c>
       <c r="B4" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>136248059</v>
       </c>
       <c r="B5" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1123,7 +1123,7 @@
         <v>136248070</v>
       </c>
       <c r="B6" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>136248188</v>
       </c>
       <c r="B7" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1555,7 +1555,7 @@
         <v>136248140</v>
       </c>
       <c r="B10" t="n">
-        <v>80589</v>
+        <v>80591</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>136248274</v>
       </c>
       <c r="B11" t="n">
-        <v>80600</v>
+        <v>80602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>136248242</v>
       </c>
       <c r="B12" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>136247961</v>
       </c>
       <c r="B13" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         <v>136247996</v>
       </c>
       <c r="B14" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136248020</v>
       </c>
       <c r="B15" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>136248030</v>
       </c>
       <c r="B16" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>136248045</v>
       </c>
       <c r="B17" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>136248055</v>
       </c>
       <c r="B18" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2585,7 +2585,7 @@
         <v>136248076</v>
       </c>
       <c r="B19" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>136248169</v>
       </c>
       <c r="B20" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2815,7 +2815,7 @@
         <v>136248204</v>
       </c>
       <c r="B21" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>136248225</v>
       </c>
       <c r="B22" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>136248261</v>
       </c>
       <c r="B23" t="n">
-        <v>58006</v>
+        <v>58008</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         <v>136247941</v>
       </c>
       <c r="B24" t="n">
-        <v>58167</v>
+        <v>58169</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92498</v>
+        <v>92503</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 41953-2025 artfynd.xlsx
+++ b/artfynd/A 41953-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136247024</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>136247035</v>
       </c>
       <c r="B26" t="n">
-        <v>92503</v>
+        <v>92505</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
